--- a/outputs/군위군_시설관리우선지역_기초지표_2025.xlsx
+++ b/outputs/군위군_시설관리우선지역_기초지표_2025.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기초지표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컬럼설명" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출방법" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="가설" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -466,6 +467,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,30 +543,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>노후경로당비율</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>고령인구1천명당_경로당수</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>위험지정세천수</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>상수도보급률</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>포트홀민원수</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>중심위도</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>중심경도</t>
         </is>
@@ -618,21 +625,24 @@
         <v>8</v>
       </c>
       <c r="O2" s="2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>13.43</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>36.237098</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>128.572805</v>
       </c>
     </row>
@@ -684,21 +694,24 @@
         <v>4</v>
       </c>
       <c r="O3" s="2" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>26.48</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>36.262449</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="U3" s="2" t="n">
         <v>128.476869</v>
       </c>
     </row>
@@ -750,21 +763,24 @@
         <v>4</v>
       </c>
       <c r="O4" s="2" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>18.66</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>36.138311</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="U4" s="2" t="n">
         <v>128.597127</v>
       </c>
     </row>
@@ -816,21 +832,24 @@
         <v>5</v>
       </c>
       <c r="O5" s="2" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>16.08</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>36.062232</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>128.660316</v>
       </c>
     </row>
@@ -882,21 +901,24 @@
         <v>4</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>24.91</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>36.169931</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="U6" s="2" t="n">
         <v>128.659686</v>
       </c>
     </row>
@@ -948,21 +970,24 @@
         <v>8</v>
       </c>
       <c r="O7" s="2" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>21.47</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>36.170471</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>128.738226</v>
       </c>
     </row>
@@ -1014,21 +1039,24 @@
         <v>4</v>
       </c>
       <c r="O8" s="2" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="P8" s="2" t="n">
         <v>21.13</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>36.101002</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>128.70965</v>
       </c>
     </row>
@@ -1080,21 +1108,24 @@
         <v>4</v>
       </c>
       <c r="O9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" s="2" t="n">
         <v>25.25</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>36.151183</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>128.82042</v>
       </c>
     </row>
@@ -1109,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1431,7 +1462,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>고령인구1천명당_경로당수</t>
+          <t>노후경로당비율</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1441,24 +1472,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>개소</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>경로당수 / 고령인구 × 1,000</t>
+          <t>노후경로당수 / 경로당수 × 100. 가설 H5 의 지표</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>위험지정세천수</t>
+          <t>고령인구1천명당_경로당수</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1468,93 +1499,115 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>소규모공공시설 위험지정 중 현행 지정된 세천 (2026-07-15 기준, 해제 1건 제외)</t>
+          <t>경로당수 / 고령인구 × 1,000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>상수도보급률</t>
+          <t>위험지정세천수</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>개소</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025년 12월 말 기준. 군 전체 값을 읍면 평균으로 구하지 말 것</t>
+          <t>소규모공공시설 위험지정 중 현행 지정된 세천 (2026-07-15 기준, 해제 1건 제외)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>포트홀민원수</t>
+          <t>상수도보급률</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>민원빅데이터 포트홀 민원 중 읍면 경계 안 지점 (2025-01~2026-10). 표본이 적어 참고용</t>
+          <t>2025년 12월 말 기준. 군 전체 값을 읍면 평균으로 구하지 말 것</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>중심위도</t>
+          <t>포트홀민원수</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>도</t>
+          <t>건</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>읍면 경계의 면적가중 중심점. EPSG:4326</t>
+          <t>민원빅데이터 포트홀 민원 중 읍면 경계 안 지점 (2025-01~2026-10). 표본이 적어 참고용</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>중심위도</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>읍면 경계의 면적가중 중심점. EPSG:4326</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>중심경도</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>실수</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>도</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>읍면 경계의 면적가중 중심점. EPSG:4326</t>
         </is>
@@ -1571,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1707,280 +1760,833 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>민원 가설</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>지표별 민원 가설은 '가설' 시트(data/hypotheses.json). 전부 미검증이며 점수·가중치를 만들지 않는다</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>■ 자료 출처</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>행정동별 연령별 주민등록인구</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>행정안전부 주민등록 인구통계 | 기준일 2025-12-31 / 2026-08-31 | https://jumin.mois.go.kr/ageStatMonth.do</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SGIS 행정구역 통계 및 경계 중 군위군(제공용 코드 22520)</t>
+          <t>행정동별 연령별 주민등록인구</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>국가데이터처(통계청) 통계지리정보서비스(SGIS) | 기준일 2024-12-31(통계) / 2025-06-30(경계 2025 2Q) | https://www.data.go.kr/data/15129688/fileData.do</t>
+          <t>행정안전부 주민등록 인구통계 | 기준일 2025-12-31 / 2026-08-31 | https://jumin.mois.go.kr/ageStatMonth.do</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>전국마을회관및경로당표준데이터 중 군위군 경로당</t>
+          <t>SGIS 행정구역 통계 및 경계 중 군위군(제공용 코드 22520)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 (공공데이터포털 표준데이터) | 기준일 2025-12-19 | https://www.data.go.kr/data/15114136/standard.do</t>
+          <t>국가데이터처(통계청) 통계지리정보서비스(SGIS) | 기준일 2024-12-31(통계) / 2025-06-30(경계 2025 2Q) | https://www.data.go.kr/data/15129688/fileData.do</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>전국소규모공공시설위험지정정보 표준데이터 중 군위군</t>
+          <t>전국마을회관및경로당표준데이터 중 군위군 경로당</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 (공공데이터포털 표준데이터) | 기준일 2026-07-15 | https://www.data.go.kr/data/15021104/standard.do</t>
+          <t>대구광역시 군위군 (공공데이터포털 표준데이터) | 기준일 2025-12-19 | https://www.data.go.kr/data/15114136/standard.do</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>대구광역시 군위군_상수도보급률 현황</t>
+          <t>전국소규모공공시설위험지정정보 표준데이터 중 군위군</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 | 기준일 2025-12-31 | https://www.data.go.kr/data/15144103/fileData.do</t>
+          <t>대구광역시 군위군 (공공데이터포털 표준데이터) | 기준일 2026-07-15 | https://www.data.go.kr/data/15021104/standard.do</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>국민권익위원회 민원빅데이터 포트홀 민원 위경도 (minPotholeLatLonInfo)</t>
+          <t>대구광역시 군위군_상수도보급률 현황</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>공공데이터포털 / 국민권익위원회 민원정보분석과 | 기준일 2025-01-01 ~ 2026-10-13 | https://www.data.go.kr/data/15114773/openapi.do</t>
+          <t>대구광역시 군위군 | 기준일 2025-12-31 | https://www.data.go.kr/data/15144103/fileData.do</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>국민권익위원회 민원빅데이터 포트홀 민원 위경도 (minPotholeLatLonInfo)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>공공데이터포털 / 국민권익위원회 민원정보분석과 | 기준일 2025-01-01 ~ 2026-10-13 | https://www.data.go.kr/data/15114773/openapi.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>군위군 읍면 행정경계</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>SGIS 추정 — 확인되지 않음 | 기준일 2025-06-30 | URL 미확인</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>■ 알아둘 점</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>표본 수</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>읍면이 8곳뿐이라 상관분석은 탐색적 수준이다. 유의성 해석에 주의</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>두 가지 인구</t>
+          <t>표본 수</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>총인구·고령인구는 주민등록(2025-12), 노령화지수·인구밀도 등은 SGIS 등록센서스(2024)다. 정의가 달라 값이 다르므로 한 지표 안에서 섞지 말 것</t>
+          <t>읍면이 8곳뿐이라 상관분석은 탐색적 수준이다. 유의성 해석에 주의</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>경계 출처</t>
+          <t>두 가지 인구</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>읍면 경계 파일의 출처가 확인되지 않았다(UNVERIFIED). 중심좌표와 포트홀 읍면 판정이 이 경계에 기대고 있다</t>
+          <t>총인구·고령인구는 주민등록(2025-12), 노령화지수·인구밀도 등은 SGIS 등록센서스(2024)다. 정의가 달라 값이 다르므로 한 지표 안에서 섞지 말 것</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>민원 자료</t>
+          <t>경계 출처</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>읍면별 생활불편 민원 건별 원자료를 확보하지 못해 민원발생률·반복민원율·처리지연율은 계산하지 않았다. 포트홀 민원 4건은 참고용</t>
+          <t>읍면 경계 파일의 출처가 확인되지 않았다(UNVERIFIED). 중심좌표와 포트홀 읍면 판정이 이 경계에 기대고 있다</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>민원 자료</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>읍면별 생활불편 민원 건별 원자료를 확보하지 못해 민원발생률·반복민원율·처리지연율은 계산하지 않았다. 포트홀 민원 4건은 참고용</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>상수도보급률</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>읍면 값만 있다. 군 전체 보급률을 읍면 평균으로 구하면 인구 가중이 빠져 틀린다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>■ 분석에서 제외한 자료</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>군위군 행정리별 인구현황 (2008~2021)</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>2021년까지만 있고 읍면 코드가 없어 8개 읍면에 붙일 수 없으며 품질 문제가 많음</t>
-        </is>
-      </c>
+      <c r="B31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>대구광역시 군위군_불법 주정차 신고 데이터</t>
+          <t>군위군 행정리별 인구현황 (2008~2021)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>신고 2건뿐이라 지표 근거로 쓸 수 없음</t>
+          <t>2021년까지만 있고 읍면 코드가 없어 8개 읍면에 붙일 수 없으며 품질 문제가 많음</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>전국주차장정보 표준데이터 중 군위군</t>
+          <t>대구광역시 군위군_불법 주정차 신고 데이터</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>엮을 가설이 없음(짝이 될 불법주정차 자료가 표본 부족)</t>
+          <t>신고 2건뿐이라 지표 근거로 쓸 수 없음</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>전국주차장정보 표준데이터 중 군위군</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>엮을 가설이 없음(짝이 될 불법주정차 자료가 표본 부족)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>대구광역시_미급수인원 현황</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>4개 읍면에만 값이 있고 상수도보급률(DATAGOKR_GUNWI_WATER_SUPPLY_RATE)과 내용이 겹침</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>■ 함께 제공하는 파일</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>군위군_시설관리우선지역_기초지표_2025.csv</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>결과표를 개방 포맷으로 (기계 판독용). 내용은 이 파일 1번 시트와 같다</t>
-        </is>
-      </c>
+      <c r="B37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>data/sources.json</t>
+          <t>군위군_시설관리우선지역_기초지표_2025.csv</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>출처·기준일·확보 상태를 구조화한 출처 레지스트리</t>
+          <t>결과표를 개방 포맷으로 (기계 판독용). 내용은 이 파일 1번 시트와 같다</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>data/sources.json</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>출처·기준일·확보 상태를 구조화한 출처 레지스트리</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>tools/prepare.py · tools/export_excel.py</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>원자료 → 정제 → 이 파일까지의 재현 코드</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>방향</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>민원 분야</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>가설</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>검증 방법</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>검증 자료</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>elderly_ratio</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>수요형</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>생활시설, 도로·보행</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>고령화율이 높은 읍면일수록 보행·이동·생활시설 관련 불편이 많을 것이다.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>고령층은 보행 안전, 의료·복지시설 접근, 대중교통 의존도가 높아 같은 시설 조건에서도 불편을 더 크게 겪는다.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>고령층은 온라인 신고 채널 이용이 적어 '접수된 민원 건수'는 오히려 적게 잡힐 수 있다(과소신고). 실제 불편과 접수 건수를 구분해 해석한다.</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>읍면별 인구 1천명당 민원건수와 고령화율의 순위상관(Spearman). 읍면 8개라 |ρ| ≥ 0.74 일 때만 우연과 구분된다. 음의 상관이면 과소신고 신호로 본다.</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>aging_index</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>수요형</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>생활시설</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>노령화지수가 높은 읍면일수록 생활시설 관련 불편이 많을 것이다 (H1 보조).</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>유소년 대비 고령인구가 많을수록 마을 단위 돌봄·쉼터·이동 지원 수요가 커진다.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>고령화율과 같은 현상을 다른 분모로 본 지표다. H1 과 함께 증거로 두 번 세지 않는다. SGIS 2024 기준이라 주민등록 인구 지표와 한 산식에서 섞지 않는다.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>H1 과 같다. H1 과 결과가 갈리면 분모(유소년 인구) 효과를 먼저 확인한다.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>density_per_km2</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>수요형</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>±</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>교통·주차, 폐기물·환경</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>인구밀도가 높은 읍면(군위읍)은 교통·주차·환경청소 민원 '건수'가 많고, 밀도가 낮은 면 지역은 시설까지의 거리에서 오는 불편이 클 것이다.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>사람과 차량이 몰린 곳에서 주차·교통·쓰레기 문제가 생긴다. 대구 살피소 제보에서도 도시 지역 처리기관은 현수막·교통·환경청소 비중이 높다(E1).</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>방향이 민원 유형마다 반대라 하나의 부호로 정할 수 없다. 건수 기준과 인구 1천명당 기준의 결과가 다를 수 있다. SGIS 인구 기준 지표다.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>민원을 분야별로 나눠 분야마다 따로 순위상관을 본다. 분야를 합친 총건수로는 검증하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>senior_center_per_1k_elderly</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>부족형</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>생활시설</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>고령인구 1천명당 경로당이 적은 읍면일수록 복지·쉼터 시설 확충을 요구하는 민원이 많을 것이다.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>시설이 낡아서 생기는 민원(노후형)과 달리, 시설이 모자라서 생기는 설치·확충 요구 민원이다.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>경로당은 마을마다 하나씩 두는 경우가 많아 인구가 적은 면일수록 1천명당 값이 높게 나온다(분모 효과). 값이 높다고 서비스가 충분하다는 뜻은 아니다.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>생활시설 분야 중 '설치·확충 요구' 민원만 골라 순위상관을 본다. 고장·보수 민원은 H5 로 보낸다.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>senior_center_old_ratio</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>노후형</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>생활시설, 조명·안전</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2000년 이전 건립 경로당 비율이 높은 읍면일수록 보수·안전 관련 민원이 많을 것이다.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>건물이 오래될수록 누수·설비 고장·안전 문제가 생기고, 이용자 대부분이 고령층이라 불편이 바로 민원으로 이어진다.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2000년 기준은 공식 기준이 아닌 프로젝트 임시값이다(SENIOR_OLD_BEFORE_YEAR). 건립연도만 있고 리모델링·보수 이력이 없어 실제 노후도와 다를 수 있다.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>보수 이력이 들어오면 노후 판정을 '건립연도'에서 '마지막 보수연도'로 바꿔 다시 센다. 그 뒤 생활시설 고장·보수 민원과 순위상관을 본다.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>FACILITY_MAINT_HISTORY, COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>drainage_risk_count</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>노후형</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>상·하수도, 도로·보행</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>위험지정 세천이 많은 읍면일수록 침수·배수·세천 정비 관련 민원이 많을 것이다.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>군이 관리가 필요하다고 지정한 세천은 집중호우 때 범람·도로 침수로 이어질 수 있다.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>군이 위험시설로 지정한 세천 목록일 뿐 배수시설(빗물받이·맨홀) 전수가 아니다. 지정사유가 원본에서 전부 공란이라 위험 정도를 구분할 수 없다.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>배수·침수 분야 민원을 장마철(6~9월)과 나머지로 나눠, 장마철 건수와의 순위상관을 본다.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>water_supply_rate</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>부족형</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>상·하수도</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>상수도보급률이 낮은 읍면일수록 급수·수질·단수 관련 민원이 많을 것이다.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>상수도가 닿지 않는 지역은 지하수·소규모 급수시설에 의존해 수질·수량 문제가 생기기 쉽다. 삼국유사면(65%)이 다른 읍면(86~99%)보다 눈에 띄게 낮다.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>읍면 값만 있다. 군 전체 보급률을 읍면 평균으로 구하지 않는다(인구 가중 아님). 관망 노후도는 이 지표에 없다.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>상·하수도 분야 민원과 순위상관을 본다. 관망 자료가 들어오면 보급률(부족형)과 관로 경년(노후형)을 나눠 본다.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>COMPLAINT_INTERNAL, WATER_SEWER_ASSET_INTERNAL</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>가설(미검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>DAEGU_SALPISO_REPORTS</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>사실(군 단위)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>군위군 살피소 제보 87건 중 현수막 37건(43%), 도로시설 13건·교통시설 13건(합 30%). 읍면 구분이 없어 읍면 가설의 검증 자료는 아니고, 군위군 민원 구성의 배경 근거로만 쓴다.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>MINWON_POTHOLE_LATLON</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>사실(표본 부족)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2025-01~2026-10 포트홀 민원 중 군위군 경계 안은 4건(우보면 2, 효령면 2)뿐이다. 읍면 비교나 상관 계산에 쓰지 않는다.</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/군위군_시설관리우선지역_기초지표_2025.xlsx
+++ b/outputs/군위군_시설관리우선지역_기초지표_2025.xlsx
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>SGIS 추정 — 확인되지 않음 | 기준일 2025-06-30 | URL 미확인</t>
+          <t>통계청 SGIS (국가데이터처) | 기준일 2025-06-30 | https://www.data.go.kr/data/15129688/fileData.do</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>읍면 경계 파일의 출처가 확인되지 않았다(UNVERIFIED). 중심좌표와 포트홀 읍면 판정이 이 경계에 기대고 있다</t>
+          <t>읍면 경계는 통계청 SGIS 행정구역 경계 2025년 2분기(기준일 2025-06-30). 2026-10-15 SGIS 원본과 8개 읍면 도형 일치 확인</t>
         </is>
       </c>
     </row>
